--- a/GATEWAY/A1#111#PROBUSSRLX2/PROBUS srl/Hippocrates/V.2.41/accreditamento-checklist_V9.0.0.xlsx
+++ b/GATEWAY/A1#111#PROBUSSRLX2/PROBUS srl/Hippocrates/V.2.41/accreditamento-checklist_V9.0.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\Desktop\Probus\accreditamento bis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\windows\Desktop\Probus\accreditamento bis\accreditamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FE190A-94AD-4FD6-BE9B-2729AB381691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64E185F4-3611-4D2E-9334-C436A3549484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="8220" windowWidth="28800" windowHeight="13815" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="8940" windowWidth="28800" windowHeight="13815" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="656">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2473,6 +2473,12 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.120.4.4.37c86dc23a518b65226d17639c8ea6840b681fe52090c4c0caf0b0ba3179e9a4.a9da98d649^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>L’errore viene segnalato a video all’utente finale, che se il programma persiste chiamerà help-desk</t>
+  </si>
+  <si>
+    <t>L’errore viene segnalato a video all’utente finale, che procederà all'inserimento del dato mancante</t>
   </si>
 </sst>
 </file>
@@ -5702,9 +5708,15 @@
       <c r="P29" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
+      <c r="Q29" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="R29" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="S29" s="32" t="s">
+        <v>654</v>
+      </c>
       <c r="T29" s="32"/>
       <c r="U29" s="33" t="s">
         <v>75</v>
@@ -9547,9 +9559,15 @@
       <c r="P132" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="Q132" s="32"/>
-      <c r="R132" s="32"/>
-      <c r="S132" s="32"/>
+      <c r="Q132" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="R132" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S132" s="32" t="s">
+        <v>655</v>
+      </c>
       <c r="T132" s="32"/>
       <c r="U132" s="33"/>
       <c r="V132" s="34"/>
@@ -9602,9 +9620,15 @@
       <c r="P133" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="Q133" s="32"/>
-      <c r="R133" s="32"/>
-      <c r="S133" s="32"/>
+      <c r="Q133" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="R133" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S133" s="32" t="s">
+        <v>655</v>
+      </c>
       <c r="T133" s="32"/>
       <c r="U133" s="33"/>
       <c r="V133" s="34"/>
@@ -9862,9 +9886,15 @@
       <c r="P139" s="32" t="s">
         <v>541</v>
       </c>
-      <c r="Q139" s="32"/>
-      <c r="R139" s="32"/>
-      <c r="S139" s="32"/>
+      <c r="Q139" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="R139" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="S139" s="32" t="s">
+        <v>655</v>
+      </c>
       <c r="T139" s="32"/>
       <c r="U139" s="33"/>
       <c r="V139" s="34"/>
@@ -19873,15 +19903,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20149,27 +20176,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -20194,9 +20215,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
